--- a/docs/StructureDefinition-BRObservacaoDescritiva-1.0.xlsx
+++ b/docs/StructureDefinition-BRObservacaoDescritiva-1.0.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -383,7 +383,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -519,7 +519,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -548,7 +548,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -628,7 +628,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -977,7 +977,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1055,7 +1055,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1140,7 +1140,7 @@
     <t>Observation.subject.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1180,7 +1180,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1203,7 +1203,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1294,7 +1294,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1373,7 +1373,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1405,7 +1405,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1464,7 +1464,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1497,7 +1497,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1509,7 +1509,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1537,7 +1537,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1617,7 +1617,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1667,7 +1667,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1700,7 +1700,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1737,7 +1737,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1759,7 +1759,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1820,7 +1820,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -2198,7 +2198,7 @@
     <col min="8" max="8" width="13.609375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.1796875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="102.26953125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="131.671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2359,7 +2359,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -3799,7 +3799,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>177</v>
       </c>
@@ -4043,7 +4043,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>199</v>
       </c>
@@ -5489,7 +5489,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>283</v>
       </c>
@@ -7655,7 +7655,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>401</v>
       </c>
@@ -7895,7 +7895,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>418</v>
       </c>
@@ -11399,12 +11399,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP76">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
